--- a/dataset/CacThanhTruyen2/labels.xlsx
+++ b/dataset/CacThanhTruyen2/labels.xlsx
@@ -651,12 +651,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>丕</t>
+          <t>出</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>U+4E15</t>
+          <t>U+51FA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -839,12 +839,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>企</t>
+          <t>壹</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>U+4F01</t>
+          <t>U+58F9</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>𢵉</t>
+          <t>𨅮</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>U+22D49</t>
+          <t>U+2816E</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2343,12 +2343,12 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>镖</t>
+          <t>𫇐</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>U+9556</t>
+          <t>U+2B1D0</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3283,12 +3283,12 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>𢵉</t>
+          <t>撫</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>U+22D49</t>
+          <t>U+64AB</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3753,12 +3753,12 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>箟</t>
+          <t>𫙔</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>U+7B9F</t>
+          <t>U+2B654</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>妸</t>
+          <t>呵</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>U+59B8</t>
+          <t>U+5475</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>喂</t>
+          <t>過</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>U+5582</t>
+          <t>U+904E</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5727,12 +5727,12 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>易</t>
+          <t>啺</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>U+6613</t>
+          <t>U+557A</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>司</t>
+          <t>𢂜</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>U+53F8</t>
+          <t>U+2209C</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>縭</t>
+          <t>摇</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>U+7E2D</t>
+          <t>U+6447</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6667,12 +6667,12 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>嗎</t>
+          <t>𠸠</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>U+55CE</t>
+          <t>U+20E20</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -7325,12 +7325,12 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>挴</t>
+          <t>哏</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>U+6334</t>
+          <t>U+54CF</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>囤</t>
+          <t>想</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>U+56E4</t>
+          <t>U+60F3</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>揭</t>
+          <t>爲</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>U+63ED</t>
+          <t>U+7232</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>孛</t>
+          <t>荸</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>U+5B5B</t>
+          <t>U+8378</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>嗺</t>
+          <t>𣈗</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>U+55FA</t>
+          <t>U+23217</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -9299,12 +9299,12 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>孛</t>
+          <t>荸</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>U+5B5B</t>
+          <t>U+8378</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -9957,12 +9957,12 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>詿</t>
+          <t>咦</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>U+8A7F</t>
+          <t>U+54A6</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -10474,12 +10474,12 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>宣</t>
+          <t>职</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>U+5BA3</t>
+          <t>U+804C</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>噫</t>
+          <t>𠱊</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>U+566B</t>
+          <t>U+20C4A</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -11038,12 +11038,12 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>悶</t>
+          <t>锄</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>U+60B6</t>
+          <t>U+9504</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -11226,12 +11226,12 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>芋</t>
+          <t>藍</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>U+828B</t>
+          <t>U+85CD</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -11837,12 +11837,12 @@
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>𥑴</t>
+          <t>碎</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>U+25474</t>
+          <t>U+788E</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -11978,12 +11978,12 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>𨨦</t>
+          <t>󱨄</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>U+28A26</t>
+          <t>U+F1A04</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>圄</t>
+          <t>𠸠</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>U+5704</t>
+          <t>U+20E20</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -13012,12 +13012,12 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>𠡏</t>
+          <t>特</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>U+2084F</t>
+          <t>U+7279</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -13106,12 +13106,12 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>𠱋</t>
+          <t>󱤮</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>U+20C4B</t>
+          <t>U+F192E</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -13435,12 +13435,12 @@
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>喟</t>
+          <t>𪠞</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>U+559F</t>
+          <t>U+2A81E</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -14187,12 +14187,12 @@
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>吏</t>
+          <t>𠘨</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>U+540F</t>
+          <t>U+20628</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -14281,12 +14281,12 @@
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>坊</t>
+          <t>餘</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>U+574A</t>
+          <t>U+9918</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>阜</t>
+          <t>中</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>U+961C</t>
+          <t>U+4E2D</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -14798,12 +14798,12 @@
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>狮</t>
+          <t>郕</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>U+72EE</t>
+          <t>U+90D5</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -15033,12 +15033,12 @@
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>宣</t>
+          <t>哭</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>U+5BA3</t>
+          <t>U+54ED</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -15503,12 +15503,12 @@
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>電</t>
+          <t>㾯</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>U+96FB</t>
+          <t>U+3FAF</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -15785,12 +15785,12 @@
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>迤</t>
+          <t>吒</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>U+8FE4</t>
+          <t>U+5412</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -15879,12 +15879,12 @@
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>𠸩</t>
+          <t>炷</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>U+20E29</t>
+          <t>U+70B7</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -15926,12 +15926,12 @@
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>呞</t>
+          <t>旹</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>U+545E</t>
+          <t>U+65F9</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -16067,12 +16067,12 @@
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>吳</t>
+          <t>硌</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>U+5433</t>
+          <t>U+784C</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -16255,12 +16255,12 @@
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>俞</t>
+          <t>𫴾</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>U+4FDE</t>
+          <t>U+2BD3E</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -16349,12 +16349,12 @@
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>诀</t>
+          <t>撟</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>U+8BC0</t>
+          <t>U+649F</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -16443,12 +16443,12 @@
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>睏</t>
+          <t>思</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>U+774F</t>
+          <t>U+601D</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -16678,12 +16678,12 @@
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>階</t>
+          <t>𠏠</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>U+968E</t>
+          <t>U+203E0</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -19357,12 +19357,12 @@
       </c>
       <c r="B403" s="2" t="inlineStr">
         <is>
-          <t>𠹖</t>
+          <t>撟</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>U+20E56</t>
+          <t>U+649F</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -19639,12 +19639,12 @@
       </c>
       <c r="B409" s="2" t="inlineStr">
         <is>
-          <t>嚼</t>
+          <t>𠻗</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>U+56BC</t>
+          <t>U+20ED7</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
@@ -20156,12 +20156,12 @@
       </c>
       <c r="B420" s="2" t="inlineStr">
         <is>
-          <t>鲐</t>
+          <t>移</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>U+9C90</t>
+          <t>U+79FB</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -20297,12 +20297,12 @@
       </c>
       <c r="B423" s="2" t="inlineStr">
         <is>
-          <t>衕</t>
+          <t>𤏤</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>U+8855</t>
+          <t>U+243E4</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -20532,12 +20532,12 @@
       </c>
       <c r="B428" s="2" t="inlineStr">
         <is>
-          <t>𡔍</t>
+          <t>𫳭</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>U+2150D</t>
+          <t>U+2BCED</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -20955,12 +20955,12 @@
       </c>
       <c r="B437" s="2" t="inlineStr">
         <is>
-          <t>掘</t>
+          <t>坭</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>U+6398</t>
+          <t>U+576D</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -21002,12 +21002,12 @@
       </c>
       <c r="B438" s="2" t="inlineStr">
         <is>
-          <t>𠀗</t>
+          <t>𪪳</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>U+20017</t>
+          <t>U+2AAB3</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
@@ -22036,12 +22036,12 @@
       </c>
       <c r="B460" s="2" t="inlineStr">
         <is>
-          <t>捕</t>
+          <t>哺</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>U+6355</t>
+          <t>U+54FA</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
@@ -22177,12 +22177,12 @@
       </c>
       <c r="B463" s="2" t="inlineStr">
         <is>
-          <t>捕</t>
+          <t>哺</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>U+6355</t>
+          <t>U+54FA</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
@@ -23540,12 +23540,12 @@
       </c>
       <c r="B492" s="2" t="inlineStr">
         <is>
-          <t>譙</t>
+          <t>讲</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>U+8B59</t>
+          <t>U+8BB2</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
@@ -23775,12 +23775,12 @@
       </c>
       <c r="B497" s="2" t="inlineStr">
         <is>
-          <t>競</t>
+          <t>繓</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>U+7AF6</t>
+          <t>U+7E53</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
@@ -24809,12 +24809,12 @@
       </c>
       <c r="B519" s="2" t="inlineStr">
         <is>
-          <t>革</t>
+          <t>󱟼</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>U+9769</t>
+          <t>U+F17FC</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
@@ -25326,12 +25326,12 @@
       </c>
       <c r="B530" s="2" t="inlineStr">
         <is>
-          <t>𡉽</t>
+          <t>𠯿</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>U+2127D</t>
+          <t>U+20BFF</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
@@ -25843,12 +25843,12 @@
       </c>
       <c r="B541" s="2" t="inlineStr">
         <is>
-          <t>昚</t>
+          <t>𫯝</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>U+661A</t>
+          <t>U+2BBDD</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
@@ -26172,12 +26172,12 @@
       </c>
       <c r="B548" s="2" t="inlineStr">
         <is>
-          <t>檗</t>
+          <t>󱡃</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>U+6A97</t>
+          <t>U+F1843</t>
         </is>
       </c>
       <c r="D548" t="inlineStr">
@@ -26689,12 +26689,12 @@
       </c>
       <c r="B559" s="2" t="inlineStr">
         <is>
-          <t>檀</t>
+          <t>喭</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>U+6A80</t>
+          <t>U+55AD</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
@@ -27112,12 +27112,12 @@
       </c>
       <c r="B568" s="2" t="inlineStr">
         <is>
-          <t>锷</t>
+          <t>鱸</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>U+9537</t>
+          <t>U+9C78</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
@@ -27770,12 +27770,12 @@
       </c>
       <c r="B582" s="2" t="inlineStr">
         <is>
-          <t>普</t>
+          <t>鱸</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>U+666E</t>
+          <t>U+9C78</t>
         </is>
       </c>
       <c r="D582" t="inlineStr">
@@ -27958,12 +27958,12 @@
       </c>
       <c r="B586" s="2" t="inlineStr">
         <is>
-          <t>彗</t>
+          <t>別</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>U+5F57</t>
+          <t>U+5225</t>
         </is>
       </c>
       <c r="D586" t="inlineStr">
@@ -28052,12 +28052,12 @@
       </c>
       <c r="B588" s="2" t="inlineStr">
         <is>
-          <t>狡</t>
+          <t>埃</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>U+72E1</t>
+          <t>U+57C3</t>
         </is>
       </c>
       <c r="D588" t="inlineStr">
@@ -28193,12 +28193,12 @@
       </c>
       <c r="B591" s="2" t="inlineStr">
         <is>
-          <t>弔</t>
+          <t>坭</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>U+5F14</t>
+          <t>U+576D</t>
         </is>
       </c>
       <c r="D591" t="inlineStr">
@@ -28240,12 +28240,12 @@
       </c>
       <c r="B592" s="2" t="inlineStr">
         <is>
-          <t>蜍</t>
+          <t>悇</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>U+870D</t>
+          <t>U+6087</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
@@ -32282,12 +32282,12 @@
       </c>
       <c r="B678" s="2" t="inlineStr">
         <is>
-          <t>妞</t>
+          <t>怒</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>U+599E</t>
+          <t>U+6012</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
@@ -32329,12 +32329,12 @@
       </c>
       <c r="B679" s="2" t="inlineStr">
         <is>
-          <t>镝</t>
+          <t>墩</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>U+955D</t>
+          <t>U+58A9</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
@@ -32658,12 +32658,12 @@
       </c>
       <c r="B686" s="2" t="inlineStr">
         <is>
-          <t>茲</t>
+          <t>苔</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>U+8332</t>
+          <t>U+82D4</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
@@ -32893,12 +32893,12 @@
       </c>
       <c r="B691" s="2" t="inlineStr">
         <is>
-          <t>吿</t>
+          <t>梔</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>U+543F</t>
+          <t>U+6894</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
@@ -33269,12 +33269,12 @@
       </c>
       <c r="B699" s="2" t="inlineStr">
         <is>
-          <t>罸</t>
+          <t>𣈙</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>U+7F78</t>
+          <t>U+23219</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
@@ -34444,12 +34444,12 @@
       </c>
       <c r="B724" s="2" t="inlineStr">
         <is>
-          <t>儗</t>
+          <t>𪺿</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>U+5117</t>
+          <t>U+2AEBF</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
@@ -36136,12 +36136,12 @@
       </c>
       <c r="B760" s="2" t="inlineStr">
         <is>
-          <t>我</t>
+          <t>拽</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>U+6211</t>
+          <t>U+62FD</t>
         </is>
       </c>
       <c r="D760" t="inlineStr">
@@ -36559,12 +36559,12 @@
       </c>
       <c r="B769" s="2" t="inlineStr">
         <is>
-          <t>時</t>
+          <t>蒔</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>U+6642</t>
+          <t>U+8494</t>
         </is>
       </c>
       <c r="D769" t="inlineStr">
@@ -38627,12 +38627,12 @@
       </c>
       <c r="B813" s="2" t="inlineStr">
         <is>
-          <t>饒</t>
+          <t>澆</t>
         </is>
       </c>
       <c r="C813" t="inlineStr">
         <is>
-          <t>U+9952</t>
+          <t>U+6F86</t>
         </is>
       </c>
       <c r="D813" t="inlineStr">
@@ -39473,12 +39473,12 @@
       </c>
       <c r="B831" s="2" t="inlineStr">
         <is>
-          <t>捥</t>
+          <t>𠲖</t>
         </is>
       </c>
       <c r="C831" t="inlineStr">
         <is>
-          <t>U+6365</t>
+          <t>U+20C96</t>
         </is>
       </c>
       <c r="D831" t="inlineStr">
@@ -39661,12 +39661,12 @@
       </c>
       <c r="B835" s="2" t="inlineStr">
         <is>
-          <t>君</t>
+          <t>特</t>
         </is>
       </c>
       <c r="C835" t="inlineStr">
         <is>
-          <t>U+541B</t>
+          <t>U+7279</t>
         </is>
       </c>
       <c r="D835" t="inlineStr">
@@ -41400,12 +41400,12 @@
       </c>
       <c r="B872" s="2" t="inlineStr">
         <is>
-          <t>昰</t>
+          <t>梔</t>
         </is>
       </c>
       <c r="C872" t="inlineStr">
         <is>
-          <t>U+6630</t>
+          <t>U+6894</t>
         </is>
       </c>
       <c r="D872" t="inlineStr">
@@ -41682,12 +41682,12 @@
       </c>
       <c r="B878" s="2" t="inlineStr">
         <is>
-          <t>𡥵</t>
+          <t>焒</t>
         </is>
       </c>
       <c r="C878" t="inlineStr">
         <is>
-          <t>U+21975</t>
+          <t>U+7112</t>
         </is>
       </c>
       <c r="D878" t="inlineStr">
@@ -41823,12 +41823,12 @@
       </c>
       <c r="B881" s="2" t="inlineStr">
         <is>
-          <t>儗</t>
+          <t>𤡌</t>
         </is>
       </c>
       <c r="C881" t="inlineStr">
         <is>
-          <t>U+5117</t>
+          <t>U+2484C</t>
         </is>
       </c>
       <c r="D881" t="inlineStr">
@@ -42528,12 +42528,12 @@
       </c>
       <c r="B896" s="2" t="inlineStr">
         <is>
-          <t>脚</t>
+          <t>悲</t>
         </is>
       </c>
       <c r="C896" t="inlineStr">
         <is>
-          <t>U+811A</t>
+          <t>U+60B2</t>
         </is>
       </c>
       <c r="D896" t="inlineStr">
